--- a/data_extactor/batch_10_fa/trimmed/batch_0012_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0012_fa_trim.xlsx
@@ -508,12 +508,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | سخن گفتن | نگارش | شنیدن فعال | یادگیری فعال | راهبردهای یادگیری | نظارت | ریاضیات</t>
+          <t>درک مطلب | تفکر انتقادی | سخن گفتن | نگارش | گوش دادن فعال | یادگیری فعال | راهبردهای یادگیری | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | زبان انگلیسی | پزشکی و دندان‌پزشکی | مدیریت و امور اداری | ریاضیات | مهندسی و فناوری</t>
+          <t>رایانه و الکترونیک | زبان انگلیسی | پزشکی و دندان‌پزشکی | مدیریت و اداره | ریاضیات | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مدیران داده‌های بالینی | تحلیل‌گران سیستم‌های رایانه‌ای | متخصصان فناوری اطلاعات سلامت و ثبّات‌های پزشکی | متخصصان مدارک و اسناد پزشکی | مدیران خدمات درمانی و بهداشتی | مربیان و مدرسان پرستاری، آموزش عالی | پرستاران دارای پروانه</t>
+          <t>مدیران داده‌های بالینی | تحلیل‌گران سیستم‌های کامپیوتری | کارشناسان فناوری اطلاعات سلامت و ثبت داده‌های پزشکی | کارشناسان و تکنسین‌های مدارک پزشکی و فناوری اطلاعات سلامت | مدیران خدمات درمانی و بهداشتی | مربیان و استادان پرستاری دانشگاه | پرستاران</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | زبان انگلیسی | مدیریت و امور اداری | مخابرات | مهندسی و فناوری | ایمنی و امنیت عمومی</t>
+          <t>رایانه و الکترونیک | زبان انگلیسی | مدیریت و اداره | مخابرات | مهندسی و فناوری | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بیان کتبی | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | درک کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بیان کتبی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>معماران شبکه رایانه‌ای | تحلیل‌گران سیستم‌های رایانه‌ای | تحلیل‌گران جرم‌یابی دیجیتال | مهندسان امنیت اطلاعات | مدیران شبکه و سیستم‌های رایانه‌ای | متخصصان ارزیابی نفوذپذیری | کارشناسان مدیریت امنیت</t>
+          <t>معماران شبکه رایانه‌ای | تحلیل‌گران سیستم‌های کامپیوتری | تحلیل‌گران جرم‌یابی دیجیتال و پاسخ به حوادث | مهندسان امنیت اطلاعات | مدیران شبکه و سیستم‌های کامپیوتری | متخصصان آزمون نفوذپذیری و ارزیابی امنیتی | کارشناسان مدیریت حراست و امنیت فیزیکی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | شنیدن فعال | سخن گفتن | یادگیری فعال | ریاضیات | نگارش | علوم پایه | نظارت | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | سخن گفتن | یادگیری فعال | ریاضیات | نگارش | علوم | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | ریاضیات | مهندسی و فناوری | زبان انگلیسی | مدیریت و امور اداری | طراحی | مخابرات</t>
+          <t>رایانه و الکترونیک | ریاضیات | مهندسی و فناوری | زبان انگلیسی | مدیریت و اداره | طراحی | مخابرات</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | روان بودن ایده‌ها | حساسیت به مسئله | استدلال ریاضی</t>
+          <t>استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | روانی ایده‌ها | حساسیت به مسئله | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مهندسان سخت‌افزار رایانه | برنامه‌نویسان رایانه | مدرسان علوم رایانه، آموزش عالی | تحلیل‌گران سیستم‌های رایانه‌ای | دانشمندان داده | ریاضیدانان | توسعه‌دهندگان نرم‌افزار</t>
+          <t>مهندسان سخت‌افزار رایانه | برنامه‌نویسان کامپیوتر | استادان علوم رایانه، آموزش عالی | تحلیل‌گران سیستم‌های کامپیوتری | دانشمندان داده | ریاضی‌دانان | توسعه‌دهندگان نرم‌افزار</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | درک مطلب | نظارت | یادگیری فعال | سخن گفتن | نگارش</t>
+          <t>تفکر انتقادی | گوش دادن فعال | درک مطلب | نظارت | یادگیری فعال | سخن گفتن | نگارش</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | مخابرات | خدمات مشتریان و خدمات فردی | مهندسی و فناوری | زبان انگلیسی | مدیریت و امور اداری</t>
+          <t>رایانه و الکترونیک | مخابرات | خدمات مشتری و شخصی | مهندسی و فناوری | زبان انگلیسی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | حساسیت به مسئله | استدلال قیاسی | بیان شفاهی | استدلال استقرایی | درک کتبی | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | حساسیت به مسئله | استدلال قیاسی | بیان شفاهی | استدلال استقرایی | درک کتبی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>معماران شبکه رایانه‌ای | متخصصان پشتیبانی کاربران رایانه | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | تحلیل‌گران امنیت اطلاعات | مدیران شبکه و سیستم‌های رایانه‌ای | متخصصان مهندسی مخابرات | نصابان و تعمیرکاران تجهیزات مخابراتی، به‌جز خطوط ارتباطی</t>
+          <t>معماران شبکه رایانه‌ای | متخصصان پشتیبانی کاربران رایانه | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | تحلیل‌گران امنیت اطلاعات | مدیران شبکه و سیستم‌های کامپیوتری | متخصصان مهندسی مخابرات | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز سیم‌بانان</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال | راهبردهای یادگیری | نظارت</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | خدمات مشتریان و خدمات فردی | مخابرات | زبان انگلیسی | آموزش و پرورش | مهندسی و فناوری</t>
+          <t>رایانه و الکترونیک | خدمات مشتری و شخصی | مخابرات | زبان انگلیسی | آموزش و پرورش | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | مرتب‌سازی اطلاعات | حساسیت به مسئله | استدلال قیاسی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>متخصصان پشتیبانی شبکه رایانه‌ای | تحلیل‌گران سیستم‌های رایانه‌ای | تعمیرکاران رایانه، خودپرداز و ماشین‌های اداری | تحلیل‌گران امنیت اطلاعات | مدیران شبکه و سیستم‌های رایانه‌ای | توسعه‌دهندگان نرم‌افزار | نصابان و تعمیرکاران تجهیزات مخابراتی، به‌جز خطوط ارتباطی</t>
+          <t>متخصصان پشتیبانی شبکه رایانه‌ای | تحلیل‌گران سیستم‌های کامپیوتری | تعمیرکاران رایانه، خودپرداز و ماشین‌های اداری | تحلیل‌گران امنیت اطلاعات | مدیران شبکه و سیستم‌های کامپیوتری | توسعه‌دهندگان نرم‌افزار | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز سیم‌بانان</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | شنیدن فعال | نگارش | سخن گفتن | یادگیری فعال | نظارت | راهبردهای یادگیری | ریاضیات</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | نگارش | سخن گفتن | یادگیری فعال | نظارت | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | درک شفاهی</t>
+          <t>درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | درک شفاهی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>متخصصان پشتیبانی شبکه رایانه‌ای | تحلیل‌گران سیستم‌های رایانه‌ای | مهندسان و معماران سیستم‌های رایانه‌ای | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | مدیران شبکه و سیستم‌های رایانه‌ای | متخصصان مهندسی مخابرات</t>
+          <t>متخصصان پشتیبانی شبکه رایانه‌ای | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | مدیران شبکه و سیستم‌های کامپیوتری | متخصصان مهندسی مخابرات</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | یادگیری فعال | سخن گفتن | نگارش | نظارت | ریاضیات</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | یادگیری فعال | سخن گفتن | نگارش | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | دید نزدیک | درک کتبی | مرتب‌سازی اطلاعات | استدلال قیاسی</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | بینایی نزدیک | درک کتبی | ترتیب‌دهی اطلاعات | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>معماران شبکه رایانه‌ای | متخصصان پشتیبانی شبکه رایانه‌ای | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | مهندسان الکترونیک، به‌جز رایانه | مدیران شبکه و سیستم‌های رایانه‌ای | نصابان و تعمیرکاران تجهیزات رادیویی، سلولی و دکل‌های مخابراتی | نصابان و تعمیرکاران تجهیزات مخابراتی، به‌جز خطوط ارتباطی</t>
+          <t>معماران شبکه رایانه‌ای | متخصصان پشتیبانی شبکه رایانه‌ای | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | مهندسان الکترونیک، به‌جز کامپیوتر | مدیران شبکه و سیستم‌های کامپیوتری | نصابان و تعمیرکاران تجهیزات رادیویی، سلولار و دکل‌های مخابراتی | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز سیم‌بانان</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | شنیدن فعال | یادگیری فعال | سخن گفتن | نظارت | نگارش | راهبردهای یادگیری | ریاضیات</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | یادگیری فعال | سخن گفتن | نظارت | نگارش | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | زبان انگلیسی | ریاضیات | مخابرات | مهندسی و فناوری | مدیریت و امور اداری</t>
+          <t>رایانه و الکترونیک | زبان انگلیسی | ریاضیات | مخابرات | مهندسی و فناوری | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | حساسیت به مسئله | استدلال استقرایی | مرتب‌سازی اطلاعات | درک شفاهی | درک کتبی | بیان کتبی</t>
+          <t>استدلال قیاسی | حساسیت به مسئله | استدلال استقرایی | ترتیب‌دهی اطلاعات | درک شفاهی | درک کتبی | بیان کتبی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>برنامه‌نویسان رایانه | تحلیل‌گران سیستم‌های رایانه‌ای | متخصصان انباره داده | معماران پایگاه داده | تحلیل‌گران امنیت اطلاعات | مدیران شبکه و سیستم‌های رایانه‌ای | توسعه‌دهندگان نرم‌افزار</t>
+          <t>برنامه‌نویسان کامپیوتر | تحلیل‌گران سیستم‌های کامپیوتری | متخصصان انباره داده | معماران پایگاه داده | تحلیل‌گران امنیت اطلاعات | مدیران شبکه و سیستم‌های کامپیوتری | توسعه‌دهندگان نرم‌افزار</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | سخن گفتن | یادگیری فعال | نگارش | نظارت | ریاضیات</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | یادگیری فعال | نگارش | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -974,17 +974,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | درک شفاهی | درک کتبی | حساسیت به مسئله | استدلال استقرایی | مرتب‌سازی اطلاعات | بیان کتبی</t>
+          <t>استدلال قیاسی | درک شفاهی | درک کتبی | حساسیت به مسئله | استدلال استقرایی | ترتیب‌دهی اطلاعات | بیان کتبی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>مکاتبهٔ ایمیلی | نشستن طولانی‌مدت پشت میز | ارتباط تلفنی | گفت‌وگوی حضوری با همکاران | اهمیت بالای دقت در کار | استقلال و آزادی عمل در تصمیم‌گیری | کار گروهی و تیمی</t>
+          <t>ایمیل | صرف زمان برای نشستن | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل شرایط محیطی | تعیین وظایف، اولویت‌ها و اهداف | سطح رقابت | تأثیر تصمیمات بر همکاران یا نتایج شرکت | ارتباط با دیگران | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>تحلیل‌گران هوش تجاری | تحلیل‌گران سیستم‌های رایانه‌ای | دانشمندان داده | متخصصان انباره داده | مدیران پایگاه داده | مدیران شبکه و سیستم‌های رایانه‌ای | توسعه‌دهندگان نرم‌افزار</t>
+          <t>تحلیل‌گران هوش تجاری | تحلیل‌گران سیستم‌های کامپیوتری | دانشمندان داده | متخصصان انباره داده | مدیران پایگاه داده | مدیران شبکه و سیستم‌های کامپیوتری | توسعه‌دهندگان نرم‌افزار</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | سخن گفتن | نگارش | یادگیری فعال | ریاضیات</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | یادگیری فعال | ریاضیات</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک کتبی | مرتب‌سازی اطلاعات | درک شفاهی | استدلال قیاسی | استدلال استقرایی | بیان کتبی | حساسیت به مسئله</t>
+          <t>درک کتبی | ترتیب‌دهی اطلاعات | درک شفاهی | استدلال قیاسی | استدلال استقرایی | بیان کتبی | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>تحلیل‌گران هوش تجاری | برنامه‌نویسان رایانه | تحلیل‌گران سیستم‌های رایانه‌ای | دانشمندان داده | مدیران پایگاه داده | معماران پایگاه داده | توسعه‌دهندگان نرم‌افزار</t>
+          <t>تحلیل‌گران هوش تجاری | برنامه‌نویسان کامپیوتر | تحلیل‌گران سیستم‌های کامپیوتری | دانشمندان داده | مدیران پایگاه داده | معماران پایگاه داده | توسعه‌دهندگان نرم‌افزار</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
